--- a/data/trans_camb/IP19C07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 6,12</t>
+          <t>-15,48; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 3,7</t>
+          <t>-19,2; 2,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 1,68</t>
+          <t>-18,54; 2,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 12,01</t>
+          <t>-4,88; 12,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 11,85</t>
+          <t>-6,07; 12,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -1,47</t>
+          <t>-12,09; -1,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,18</t>
+          <t>-8,14; 5,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 4,04</t>
+          <t>-10,36; 3,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -0,63</t>
+          <t>-12,54; -0,8</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,01; 124,37</t>
+          <t>-80,02; 115,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 117,91</t>
+          <t>-100,0; 165,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,75</t>
+          <t>-100,0; 89,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 898,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 91,13</t>
+          <t>-66,61; 120,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,62; 84,87</t>
+          <t>-85,21; 106,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,89</t>
+          <t>-100,0; 41,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 1,07</t>
+          <t>-7,62; 0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 0,66</t>
+          <t>-7,53; 0,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 0,52</t>
+          <t>-8,72; -0,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 2,04</t>
+          <t>-6,55; 1,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -2,86</t>
+          <t>-10,32; -2,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -1,07</t>
+          <t>-8,53; -0,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,23</t>
+          <t>-5,84; 0,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -1,91</t>
+          <t>-7,72; -1,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -1,8</t>
+          <t>-7,38; -1,4</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,03; 18,42</t>
+          <t>-59,73; 12,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 11,71</t>
+          <t>-58,61; 10,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 10,58</t>
+          <t>-63,99; 5,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 26,11</t>
+          <t>-53,61; 27,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,18; -32,68</t>
+          <t>-80,54; -26,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,48; -11,15</t>
+          <t>-69,0; -4,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 2,25</t>
+          <t>-47,61; 3,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,59; -20,06</t>
+          <t>-63,38; -19,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,3; -18,52</t>
+          <t>-62,81; -17,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 9,83</t>
+          <t>-9,35; 10,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 4,75</t>
+          <t>-13,57; 5,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 5,0</t>
+          <t>-14,1; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 12,74</t>
+          <t>-4,85; 13,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 5,81</t>
+          <t>-10,63; 6,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 1,87</t>
+          <t>-12,77; 2,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 9,06</t>
+          <t>-4,64; 9,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 2,8</t>
+          <t>-9,42; 3,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 0,75</t>
+          <t>-11,05; 0,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 85,63</t>
+          <t>-44,91; 97,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,2; 48,45</t>
+          <t>-64,86; 51,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 46,21</t>
+          <t>-64,07; 47,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 154,68</t>
+          <t>-30,43; 169,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 72,94</t>
+          <t>-62,72; 87,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 33,18</t>
+          <t>-71,46; 36,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 83,78</t>
+          <t>-25,32; 82,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 25,07</t>
+          <t>-53,44; 27,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 9,07</t>
+          <t>-60,03; 9,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,16</t>
+          <t>-6,6; 1,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,41</t>
+          <t>-8,03; -0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -0,72</t>
+          <t>-8,19; -0,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,41</t>
+          <t>-3,89; 3,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,37</t>
+          <t>-7,2; -0,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -1,11</t>
+          <t>-7,31; -1,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,39</t>
+          <t>-3,95; 1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,63</t>
+          <t>-6,88; -1,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -2,2</t>
+          <t>-6,95; -2,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 11,65</t>
+          <t>-45,46; 14,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,74; -4,1</t>
+          <t>-54,28; -4,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,5; -5,63</t>
+          <t>-55,66; -8,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 41,55</t>
+          <t>-32,63; 39,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,08; -14,62</t>
+          <t>-62,73; -11,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,67; -12,31</t>
+          <t>-62,02; -11,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 13,27</t>
+          <t>-31,7; 11,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -16,19</t>
+          <t>-53,69; -18,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -22,85</t>
+          <t>-56,04; -20,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 5,47</t>
+          <t>-15,85; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 2,96</t>
+          <t>-18,26; 2,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 2,23</t>
+          <t>-19,13; 0,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 12,76</t>
+          <t>-6,03; 12,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 12,36</t>
+          <t>-5,98; 11,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -1,46</t>
+          <t>-12,41; -1,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 5,91</t>
+          <t>-7,91; 5,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 3,91</t>
+          <t>-10,24; 4,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -0,8</t>
+          <t>-12,45; -0,67</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 115,51</t>
+          <t>-80,4; 89,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 165,84</t>
+          <t>-100,0; 158,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 89,58</t>
+          <t>-100,0; 32,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 120,11</t>
+          <t>-65,01; 99,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 106,93</t>
+          <t>-86,85; 120,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,87</t>
+          <t>-100,0; 16,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,82</t>
+          <t>-7,55; 0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 0,84</t>
+          <t>-7,68; 1,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,05</t>
+          <t>-8,52; 0,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 1,87</t>
+          <t>-6,48; 1,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -2,49</t>
+          <t>-10,06; -2,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -0,47</t>
+          <t>-8,96; -0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,23</t>
+          <t>-5,93; 0,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -1,97</t>
+          <t>-7,78; -1,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -1,4</t>
+          <t>-7,59; -1,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 12,25</t>
+          <t>-58,8; 9,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,61; 10,47</t>
+          <t>-57,81; 14,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 5,26</t>
+          <t>-64,22; 2,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 27,73</t>
+          <t>-53,11; 21,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,54; -26,7</t>
+          <t>-78,86; -31,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,0; -4,24</t>
+          <t>-69,93; -9,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,61; 3,11</t>
+          <t>-48,81; 3,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,38; -19,52</t>
+          <t>-63,41; -16,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,81; -17,55</t>
+          <t>-61,65; -15,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 10,61</t>
+          <t>-10,35; 8,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 5,07</t>
+          <t>-13,96; 5,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,35</t>
+          <t>-13,94; 4,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 13,18</t>
+          <t>-4,47; 14,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 6,65</t>
+          <t>-10,36; 6,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 2,04</t>
+          <t>-13,43; 1,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,44</t>
+          <t>-4,43; 8,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 3,18</t>
+          <t>-10,03; 3,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 0,57</t>
+          <t>-11,82; 0,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 97,18</t>
+          <t>-47,29; 78,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,86; 51,49</t>
+          <t>-65,44; 55,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 47,55</t>
+          <t>-61,39; 46,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 169,99</t>
+          <t>-26,35; 166,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 87,31</t>
+          <t>-58,46; 82,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 36,02</t>
+          <t>-73,32; 26,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 82,17</t>
+          <t>-26,45; 80,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 27,6</t>
+          <t>-55,78; 27,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 9,33</t>
+          <t>-61,31; 9,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,34</t>
+          <t>-6,23; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,55</t>
+          <t>-7,75; -0,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,19; -0,93</t>
+          <t>-8,13; -0,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,43</t>
+          <t>-3,38; 3,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -0,97</t>
+          <t>-7,59; -1,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -1,21</t>
+          <t>-7,37; -1,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,12</t>
+          <t>-3,88; 1,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -1,98</t>
+          <t>-6,7; -1,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -2,04</t>
+          <t>-6,93; -1,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 14,07</t>
+          <t>-45,41; 11,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -4,24</t>
+          <t>-54,44; -0,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,66; -8,06</t>
+          <t>-56,97; -3,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 39,54</t>
+          <t>-28,93; 43,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -11,96</t>
+          <t>-63,7; -14,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,02; -11,9</t>
+          <t>-62,85; -11,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 11,17</t>
+          <t>-31,61; 13,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -18,39</t>
+          <t>-53,27; -17,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -20,89</t>
+          <t>-55,45; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-4,74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-9,21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-8,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,6</t>
+          <t>-6,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 5,46</t>
+          <t>-5,1; 12,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 2,93</t>
+          <t>-5,54; 11,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 0,67</t>
+          <t>-12,27; -1,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 12,03</t>
+          <t>-14,5; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 11,4</t>
+          <t>-17,16; 3,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -1,48</t>
+          <t>-16,71; 2,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 5,23</t>
+          <t>-7,87; 5,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 4,58</t>
+          <t>-9,54; 4,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,45; -0,67</t>
+          <t>-12,67; -0,3</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58,1%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-36,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-70,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-66,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>58,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>38,04%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-63,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-73,56%</t>
+          <t>-72,32%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 89,04</t>
+          <t>-80,62; 898,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,01; 124,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 117,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 79,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,01; 99,52</t>
+          <t>-64,46; 91,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,85; 120,06</t>
+          <t>-86,62; 84,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,78</t>
+          <t>-100,0; 33,8</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,46</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,35</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,32</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,71</t>
+          <t>-4,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,54</t>
+          <t>-4,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,77</t>
+          <t>-6,59; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 1,12</t>
+          <t>-10,41; -2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 0,05</t>
+          <t>-8,6; -0,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 1,73</t>
+          <t>-7,67; 1,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -2,94</t>
+          <t>-7,49; 0,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -0,97</t>
+          <t>-7,86; 0,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,22</t>
+          <t>-5,86; 0,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -1,59</t>
+          <t>-7,65; -1,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,55</t>
+          <t>-7,2; -1,49</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-23,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-61,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-43,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-31,25%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-31,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-40,16%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-23,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-61,94%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,16%</t>
+          <t>-38,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,5%</t>
+          <t>-41,21%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 9,82</t>
+          <t>-53,59; 26,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 14,81</t>
+          <t>-81,18; -32,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,22; 2,04</t>
+          <t>-67,36; -8,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,11; 21,0</t>
+          <t>-59,03; 18,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,86; -31,98</t>
+          <t>-57,33; 11,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,93; -9,69</t>
+          <t>-61,71; 17,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 3,44</t>
+          <t>-49,31; 2,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,41; -16,31</t>
+          <t>-63,59; -20,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,65; -15,96</t>
+          <t>-60,22; -16,42</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,74</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,69</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-4,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 8,93</t>
+          <t>-5,16; 12,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 5,07</t>
+          <t>-11,15; 5,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 4,62</t>
+          <t>-12,86; 2,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 14,2</t>
+          <t>-9,23; 9,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 6,16</t>
+          <t>-13,76; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 1,91</t>
+          <t>-13,24; 4,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 8,93</t>
+          <t>-4,48; 9,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 3,11</t>
+          <t>-9,65; 2,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 0,7</t>
+          <t>-11,32; 1,22</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-36,56%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-28,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-24,99%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-15,47%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-40,72%</t>
+          <t>-25,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,51%</t>
+          <t>-31,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 78,53</t>
+          <t>-31,77; 154,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,44; 55,47</t>
+          <t>-63,71; 72,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,39; 46,4</t>
+          <t>-70,03; 44,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 166,51</t>
+          <t>-45,57; 85,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 82,01</t>
+          <t>-65,2; 48,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,32; 26,6</t>
+          <t>-61,97; 46,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 80,89</t>
+          <t>-26,44; 83,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 27,64</t>
+          <t>-53,04; 25,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 9,17</t>
+          <t>-61,18; 13,15</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,34</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,26</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,17</t>
+          <t>-3,88; 3,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -0,2</t>
+          <t>-7,89; -1,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -0,42</t>
+          <t>-7,66; -0,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,51</t>
+          <t>-6,7; 1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,17</t>
+          <t>-7,99; -0,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -1,02</t>
+          <t>-8,17; -0,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,36</t>
+          <t>-3,82; 1,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; -1,74</t>
+          <t>-6,61; -1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,95</t>
+          <t>-6,78; -1,81</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-1,37%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-43,3%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-39,55%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-20,81%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-33,16%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,37%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-43,3%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-42,53%</t>
+          <t>-35,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-40,13%</t>
+          <t>-37,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 11,58</t>
+          <t>-32,19; 41,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -0,01</t>
+          <t>-64,08; -14,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,97; -3,72</t>
+          <t>-61,28; -8,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 43,2</t>
+          <t>-46,71; 11,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,7; -14,02</t>
+          <t>-56,74; -4,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -11,88</t>
+          <t>-56,65; -2,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 13,8</t>
+          <t>-30,64; 13,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,27; -17,23</t>
+          <t>-52,34; -16,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,45; -18,78</t>
+          <t>-54,68; -19,02</t>
         </is>
       </c>
     </row>
